--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,6 +208,30 @@
   </si>
   <si>
     <t>v.Good</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Tired</t>
+  </si>
+  <si>
+    <t>Happy</t>
+  </si>
+  <si>
+    <t>not Satsfied</t>
+  </si>
+  <si>
+    <t>mentally tired</t>
+  </si>
+  <si>
+    <t>not ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">free day convert into busy day </t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1097,9 @@
       <c r="M7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N7" s="17"/>
+      <c r="N7" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="13">
@@ -1115,9 +1141,11 @@
         <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N8" s="17"/>
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13">
@@ -1161,7 +1189,9 @@
       <c r="M9" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N9" s="17"/>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13">
@@ -1177,7 +1207,7 @@
         <v>120</v>
       </c>
       <c r="E10" s="14">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="F10" s="14">
         <v>350</v>
@@ -1190,144 +1220,254 @@
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1010</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>430</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N10" s="17"/>
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13">
         <v>46254</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="B11" s="14">
+        <v>360</v>
+      </c>
+      <c r="C11" s="14">
+        <v>20</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>120</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>6</v>
+      </c>
+      <c r="H11" s="14">
+        <v>180</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
+        <v>340</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="M11" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N11" s="17"/>
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13">
         <v>46255</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="B12" s="14">
+        <v>300</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>180</v>
+      </c>
+      <c r="E12" s="14">
+        <v>90</v>
+      </c>
+      <c r="F12" s="14">
+        <v>300</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>180</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13">
         <v>46256</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>20</v>
+      </c>
+      <c r="D13" s="14">
+        <v>240</v>
+      </c>
+      <c r="E13" s="14">
+        <v>120</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>300</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13">
         <v>46257</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
+        <v>150</v>
+      </c>
+      <c r="E14" s="14">
+        <v>150</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>180</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13">
         <v>46258</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>120</v>
+      </c>
+      <c r="F15" s="14">
+        <v>240</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>180</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13">

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,18 @@
   </si>
   <si>
     <t xml:space="preserve">free day convert into busy day </t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>feel weak</t>
+  </si>
+  <si>
+    <t>V.Good</t>
+  </si>
+  <si>
+    <t>bit tired</t>
   </si>
 </sst>
 </file>
@@ -1417,7 +1429,7 @@
         <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N14" s="17" t="s">
         <v>62</v>
@@ -1473,49 +1485,93 @@
       <c r="A16" s="13">
         <v>46259</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="B16" s="14">
+        <v>300</v>
+      </c>
+      <c r="C16" s="14">
+        <v>10</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>120</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>200</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13">
         <v>46260</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="B17" s="14">
+        <v>360</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>180</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13">

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,12 @@
   </si>
   <si>
     <t>bit tired</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>feel tense</t>
   </si>
 </sst>
 </file>
@@ -1577,25 +1583,47 @@
       <c r="A18" s="13">
         <v>46261</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="B18" s="14">
+        <v>360</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>360</v>
+      </c>
+      <c r="G18" s="14">
+        <v>6</v>
+      </c>
+      <c r="H18" s="14">
+        <v>300</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13">

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,12 @@
   </si>
   <si>
     <t>feel tense</t>
+  </si>
+  <si>
+    <t>feel low</t>
+  </si>
+  <si>
+    <t>medical issues</t>
   </si>
 </sst>
 </file>
@@ -1629,73 +1635,139 @@
       <c r="A19" s="13">
         <v>46262</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="B19" s="14">
+        <v>360</v>
+      </c>
+      <c r="C19" s="14">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>120</v>
+      </c>
+      <c r="F19" s="14">
+        <v>240</v>
+      </c>
+      <c r="G19" s="14">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14">
+        <v>360</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13">
         <v>46263</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>180</v>
+      </c>
+      <c r="E20" s="14">
+        <v>240</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>400</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13">
         <v>46264</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="B21" s="14">
+        <v>360</v>
+      </c>
+      <c r="C21" s="14">
+        <v>20</v>
+      </c>
+      <c r="D21" s="14">
+        <v>180</v>
+      </c>
+      <c r="E21" s="14">
+        <v>200</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>240</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13">

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>medical issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discuss about project </t>
   </si>
 </sst>
 </file>
@@ -1700,15 +1703,15 @@
         <v>0</v>
       </c>
       <c r="H20" s="14">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>1260</v>
+        <v>980</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>460</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>49</v>
@@ -1773,138 +1776,282 @@
       <c r="A22" s="13">
         <v>46265</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="B22" s="14">
+        <v>360</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>200</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>240</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>300</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B23" s="14">
+        <v>360</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>250</v>
+      </c>
+      <c r="E23" s="14">
+        <v>240</v>
+      </c>
+      <c r="F23" s="14">
+        <v>420</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B24" s="14">
+        <v>400</v>
+      </c>
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
+      <c r="D24" s="14">
+        <v>240</v>
+      </c>
+      <c r="E24" s="14">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <v>360</v>
+      </c>
+      <c r="G24" s="14">
+        <v>6</v>
+      </c>
+      <c r="H24" s="14">
+        <v>60</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B25" s="14">
+        <v>370</v>
+      </c>
+      <c r="C25" s="14">
+        <v>10</v>
+      </c>
+      <c r="D25" s="14">
+        <v>90</v>
+      </c>
+      <c r="E25" s="14">
+        <v>120</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5</v>
+      </c>
+      <c r="H25" s="14">
+        <v>120</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>120</v>
+      </c>
+      <c r="F26" s="14">
+        <v>420</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>330</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>240</v>
+      </c>
+      <c r="E27" s="14">
+        <v>280</v>
+      </c>
+      <c r="F27" s="14">
+        <v>60</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>420</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
+      <c r="A28" s="13">
+        <v>46271</v>
+      </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -1926,7 +2073,9 @@
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
+      <c r="A29" s="13">
+        <v>46272</v>
+      </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -1948,7 +2097,9 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
+      <c r="A30" s="13">
+        <v>46273</v>
+      </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -1970,7 +2121,9 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
+      <c r="A31" s="13">
+        <v>46274</v>
+      </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
@@ -1992,7 +2145,9 @@
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
+      <c r="A32" s="13">
+        <v>46275</v>
+      </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -2014,7 +2169,9 @@
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
+      <c r="A33" s="13">
+        <v>46276</v>
+      </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
@@ -2036,7 +2193,9 @@
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
+      <c r="A34" s="13">
+        <v>46277</v>
+      </c>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
@@ -2058,7 +2217,9 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
+      <c r="A35" s="13">
+        <v>46278</v>
+      </c>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
@@ -2080,7 +2241,9 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
+      <c r="A36" s="13">
+        <v>46279</v>
+      </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
@@ -2102,7 +2265,9 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
+      <c r="A37" s="13">
+        <v>46280</v>
+      </c>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -2124,7 +2289,9 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
+      <c r="A38" s="13">
+        <v>46281</v>
+      </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -2146,7 +2313,9 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
+      <c r="A39" s="13">
+        <v>46282</v>
+      </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
@@ -2168,7 +2337,9 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
+      <c r="A40" s="13">
+        <v>46283</v>
+      </c>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
@@ -2190,7 +2361,9 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
+      <c r="A41" s="13">
+        <v>46284</v>
+      </c>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -2212,7 +2385,9 @@
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
+      <c r="A42" s="13">
+        <v>46285</v>
+      </c>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -2234,7 +2409,9 @@
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
+      <c r="A43" s="13">
+        <v>46286</v>
+      </c>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -2256,7 +2433,9 @@
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
+      <c r="A44" s="13">
+        <v>46287</v>
+      </c>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
@@ -2278,7 +2457,9 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
+      <c r="A45" s="13">
+        <v>46288</v>
+      </c>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,12 @@
   </si>
   <si>
     <t xml:space="preserve">discuss about project </t>
+  </si>
+  <si>
+    <t>linkedinprofille update</t>
+  </si>
+  <si>
+    <t>exhausted</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1096,7 @@
         <v>480</v>
       </c>
       <c r="C7" s="14">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D7" s="14">
         <v>180</v>
@@ -1109,11 +1115,11 @@
       </c>
       <c r="I7" s="15">
         <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
-        <v>1040</v>
+        <v>1140</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>49</v>
@@ -1136,7 +1142,7 @@
         <v>360</v>
       </c>
       <c r="C8" s="14">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D8" s="14">
         <v>200</v>
@@ -1155,11 +1161,11 @@
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>980</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>460</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>58</v>
@@ -1182,7 +1188,7 @@
         <v>300</v>
       </c>
       <c r="C9" s="14">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D9" s="14">
         <v>240</v>
@@ -1201,11 +1207,11 @@
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1200</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>49</v>
@@ -1228,7 +1234,7 @@
         <v>300</v>
       </c>
       <c r="C10" s="14">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D10" s="14">
         <v>120</v>
@@ -1247,11 +1253,11 @@
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1080</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>360</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
@@ -1274,7 +1280,7 @@
         <v>360</v>
       </c>
       <c r="C11" s="14">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D11" s="14">
         <v>120</v>
@@ -1293,11 +1299,11 @@
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>240</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>59</v>
@@ -1320,7 +1326,7 @@
         <v>300</v>
       </c>
       <c r="C12" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D12" s="14">
         <v>180</v>
@@ -1339,11 +1345,11 @@
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1140</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>
@@ -1366,7 +1372,7 @@
         <v>420</v>
       </c>
       <c r="C13" s="14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D13" s="14">
         <v>240</v>
@@ -1385,11 +1391,11 @@
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1100</v>
+        <v>1140</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>49</v>
@@ -1412,7 +1418,7 @@
         <v>420</v>
       </c>
       <c r="C14" s="14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D14" s="14">
         <v>150</v>
@@ -1431,11 +1437,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>960</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>58</v>
@@ -1458,7 +1464,7 @@
         <v>420</v>
       </c>
       <c r="C15" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D15" s="14">
         <v>120</v>
@@ -1467,7 +1473,7 @@
         <v>120</v>
       </c>
       <c r="F15" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
@@ -1477,11 +1483,11 @@
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1100</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>49</v>
@@ -1504,7 +1510,7 @@
         <v>300</v>
       </c>
       <c r="C16" s="14">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D16" s="14">
         <v>120</v>
@@ -1513,7 +1519,7 @@
         <v>120</v>
       </c>
       <c r="F16" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G16" s="14">
         <v>5</v>
@@ -1523,11 +1529,11 @@
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1080</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>59</v>
@@ -1550,7 +1556,7 @@
         <v>360</v>
       </c>
       <c r="C17" s="14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D17" s="14">
         <v>120</v>
@@ -1559,7 +1565,7 @@
         <v>120</v>
       </c>
       <c r="F17" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G17" s="14">
         <v>5</v>
@@ -1569,11 +1575,11 @@
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1120</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>69</v>
@@ -1596,7 +1602,7 @@
         <v>360</v>
       </c>
       <c r="C18" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D18" s="14">
         <v>60</v>
@@ -1605,7 +1611,7 @@
         <v>60</v>
       </c>
       <c r="F18" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G18" s="14">
         <v>6</v>
@@ -1642,7 +1648,7 @@
         <v>360</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D19" s="14">
         <v>120</v>
@@ -1651,7 +1657,7 @@
         <v>120</v>
       </c>
       <c r="F19" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G19" s="14">
         <v>4</v>
@@ -1688,7 +1694,7 @@
         <v>420</v>
       </c>
       <c r="C20" s="14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D20" s="14">
         <v>180</v>
@@ -1707,11 +1713,11 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>980</v>
+        <v>1020</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>49</v>
@@ -1734,7 +1740,7 @@
         <v>360</v>
       </c>
       <c r="C21" s="14">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D21" s="14">
         <v>180</v>
@@ -1753,11 +1759,11 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>1070</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>370</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>73</v>
@@ -1780,7 +1786,7 @@
         <v>360</v>
       </c>
       <c r="C22" s="14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D22" s="14">
         <v>200</v>
@@ -1789,7 +1795,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="14">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="G22" s="14">
         <v>6</v>
@@ -1799,11 +1805,11 @@
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1400</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>49</v>
@@ -1826,7 +1832,7 @@
         <v>360</v>
       </c>
       <c r="C23" s="14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D23" s="14">
         <v>250</v>
@@ -1835,7 +1841,7 @@
         <v>240</v>
       </c>
       <c r="F23" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G23" s="14">
         <v>7</v>
@@ -1845,11 +1851,11 @@
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>1390</v>
+        <v>1410</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>49</v>
@@ -1872,7 +1878,7 @@
         <v>400</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D24" s="14">
         <v>240</v>
@@ -1881,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G24" s="14">
         <v>6</v>
@@ -1891,11 +1897,11 @@
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1120</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>59</v>
@@ -1918,7 +1924,7 @@
         <v>370</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D25" s="14">
         <v>90</v>
@@ -1927,21 +1933,21 @@
         <v>120</v>
       </c>
       <c r="F25" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G25" s="14">
         <v>5</v>
       </c>
       <c r="H25" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1040</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>49</v>
@@ -1964,7 +1970,7 @@
         <v>360</v>
       </c>
       <c r="C26" s="14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D26" s="14">
         <v>120</v>
@@ -1973,21 +1979,21 @@
         <v>120</v>
       </c>
       <c r="F26" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G26" s="14">
         <v>7</v>
       </c>
       <c r="H26" s="14">
-        <v>330</v>
+        <v>90</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>1350</v>
+        <v>1130</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>310</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>49</v>
@@ -2010,7 +2016,7 @@
         <v>420</v>
       </c>
       <c r="C27" s="14">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D27" s="14">
         <v>240</v>
@@ -2019,21 +2025,21 @@
         <v>280</v>
       </c>
       <c r="F27" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>420</v>
+        <v>120</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>1440</v>
+        <v>1230</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>58</v>
@@ -2052,49 +2058,93 @@
       <c r="A28" s="13">
         <v>46271</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>120</v>
+      </c>
+      <c r="D28" s="14">
+        <v>300</v>
+      </c>
+      <c r="E28" s="14">
+        <v>240</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13">
         <v>46272</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="B29" s="14">
+        <v>300</v>
+      </c>
+      <c r="C29" s="14">
+        <v>90</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>120</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>90</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13">

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,21 @@
   </si>
   <si>
     <t>exhausted</t>
+  </si>
+  <si>
+    <t>tired</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Worked on database, C++, Python extra codes.</t>
+  </si>
+  <si>
+    <t>Give CA of database sucessfully and parctice for freshers party</t>
   </si>
 </sst>
 </file>
@@ -1999,7 +2014,7 @@
         <v>49</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>67</v>
@@ -2146,53 +2161,97 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
         <v>46273</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="B30" s="14">
+        <v>300</v>
+      </c>
+      <c r="C30" s="14">
+        <v>100</v>
+      </c>
+      <c r="D30" s="14">
+        <v>240</v>
+      </c>
+      <c r="E30" s="14">
+        <v>120</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>100</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="13">
         <v>46274</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="B31" s="14">
+        <v>300</v>
+      </c>
+      <c r="C31" s="14">
+        <v>90</v>
+      </c>
+      <c r="D31" s="14">
+        <v>200</v>
+      </c>
+      <c r="E31" s="14">
+        <v>120</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>90</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13">
@@ -2231,10 +2290,6 @@
       <c r="H33" s="14"/>
       <c r="I33" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K33" s="16"/>
@@ -10371,7 +10426,7 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J32 J34:J401">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,12 @@
   </si>
   <si>
     <t>Give CA of database sucessfully and parctice for freshers party</t>
+  </si>
+  <si>
+    <t>Exhauted but happy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">todays enjoyed freshers party  </t>
   </si>
 </sst>
 </file>
@@ -2253,29 +2259,51 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="13">
         <v>46275</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="B32" s="14">
+        <v>300</v>
+      </c>
+      <c r="C32" s="14">
+        <v>200</v>
+      </c>
+      <c r="D32" s="14">
+        <v>60</v>
+      </c>
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>50</v>
+      </c>
+      <c r="G32" s="14">
+        <v>1</v>
+      </c>
+      <c r="H32" s="14">
+        <v>300</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13">

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,6 +286,15 @@
   </si>
   <si>
     <t xml:space="preserve">todays enjoyed freshers party  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exhauted </t>
+  </si>
+  <si>
+    <t>lil bit hectic</t>
+  </si>
+  <si>
+    <t>take ride</t>
   </si>
 </sst>
 </file>
@@ -2309,45 +2318,89 @@
       <c r="A33" s="13">
         <v>46276</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+      <c r="B33" s="14">
+        <v>320</v>
+      </c>
+      <c r="C33" s="14">
+        <v>240</v>
+      </c>
+      <c r="D33" s="14">
+        <v>90</v>
+      </c>
+      <c r="E33" s="14">
+        <v>120</v>
+      </c>
+      <c r="F33" s="14">
+        <v>350</v>
+      </c>
+      <c r="G33" s="14">
+        <v>7</v>
+      </c>
+      <c r="H33" s="14">
+        <v>90</v>
+      </c>
+      <c r="I33" s="15">
+        <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
+        <v>1210</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13">
         <v>46277</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="B34" s="14">
+        <v>300</v>
+      </c>
+      <c r="C34" s="14">
+        <v>90</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>360</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13">
